--- a/ConcastCRMFramework/TestData/TestSriptData.xlsx
+++ b/ConcastCRMFramework/TestData/TestSriptData.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7625B297-777F-4C08-BFC6-FFD6EF5D21D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DCCB0D11-5E23-435A-8BD2-A84BBA4CBE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A50F9C06-460B-475F-A45C-2F13B8F2B36F}"/>
   </bookViews>
@@ -13,7 +13,7 @@
     <sheet name="Contact" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:P8"/>
+  <oleSize ref="A1:P18"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
